--- a/inventory/files/2026-W40/STA_UK_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_UK_AUTO_2026-W40.xlsx
@@ -1539,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="14" min="1" max="1"/>
@@ -1694,47 +1694,47 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13852</v>
+        <v>12558</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-TRKITA</t>
+          <t>AH-RCTIRE10A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1751</v>
+        <v>806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AH-RCTIRE10A</t>
+          <t>AH-RCPL-B14A</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1272</v>
+        <v>760</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-RCPL-B14A</t>
+          <t>AH-RCPAINTA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>791</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AH-RCPAINTA</t>
+          <t>AH-RCWHL14A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14">
@@ -1744,37 +1744,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>261</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-PROPAINTKITA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AH-MICRTOWEL12A</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>AH-PROPAINTKITA</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/inventory/files/2026-W40/STA_UK_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_UK_AUTO_2026-W40.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12558</v>
+        <v>12521</v>
       </c>
     </row>
     <row r="10">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>806</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="12">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
